--- a/Resources/Sheet/KeHoachBaoDamQuanY.xlsx
+++ b/Resources/Sheet/KeHoachBaoDamQuanY.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123456789\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A4339E-F68B-44DC-91FE-F18F6BDF29FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B065D0-6FC8-46FF-80D3-13890BDA0152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="KeHoachBaoDamQuanY" sheetId="11" r:id="rId1"/>
+    <sheet name="KeHoachBaoDamQuanY" sheetId="12" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -287,6 +287,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -295,33 +322,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,110 +597,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16477339-0073-4BED-AC33-D0E2A9630693}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C05F80-CC1F-4AFA-9FAB-E49B7233EB8A}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="4" max="4" width="38.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="15" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="16"/>
-      <c r="M1" s="17"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="11" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="9" t="s">
+      <c r="I2" s="11"/>
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="G3" s="11"/>
+      <c r="H3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="10"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
       <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3">
@@ -710,29 +707,25 @@
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="1">
         <f>ROUND(C5*D5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="4">
-        <v>20</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="1">
-        <f t="shared" ref="G5:G10" si="0">ROUND(E5*F5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0.5</v>
-      </c>
+        <f>ROUND(E5*F5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="1">
-        <f t="shared" ref="I5:I10" si="1">ROUND(H5*C5/100,0)</f>
+        <f>ROUND(H5*C5/100,0)</f>
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" ref="J5:J10" si="2">ROUND(E5+I5,0)</f>
+        <f>ROUND(E5+I5,0)</f>
         <v>0</v>
       </c>
       <c r="K5" s="5">
@@ -756,43 +749,37 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>20</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="1">
-        <f>ROUND(C6*D6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>20</v>
-      </c>
+        <f t="shared" ref="E6:E10" si="0">ROUND(C6*D6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4"/>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0.5</v>
-      </c>
+        <f t="shared" ref="G6:G10" si="1">ROUND(E6*F6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I6:I10" si="2">ROUND(H6*C6/100,0)</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J6:J10" si="3">ROUND(E6+I6,0)</f>
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <f t="shared" ref="K6:K10" si="3">ROUNDUP(J6/2,0)</f>
+        <f t="shared" ref="K6:K10" si="4">ROUNDUP(J6/2,0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <f t="shared" ref="L6:L10" si="4">J6-K6</f>
+        <f t="shared" ref="L6:L10" si="5">J6-K6</f>
         <v>0</v>
       </c>
       <c r="M6" s="5">
-        <f t="shared" ref="M6:M10" si="5">J6</f>
+        <f t="shared" ref="M6:M10" si="6">J6</f>
         <v>0</v>
       </c>
     </row>
@@ -804,43 +791,37 @@
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>19</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="1">
-        <f>ROUND(C7*D7/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>20</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0.5</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -852,43 +833,37 @@
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>17</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="1">
-        <f>ROUND(C8*D8/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>20</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0.5</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4"/>
       <c r="I8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -910,34 +885,30 @@
         <f>E5-E6-E7-E8</f>
         <v>0</v>
       </c>
-      <c r="F9" s="4">
-        <v>20</v>
-      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.5</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4"/>
       <c r="I9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -950,48 +921,48 @@
       </c>
       <c r="C10" s="1">
         <f>C5</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1">
-        <f>ROUND(C10*D10/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>20</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.5</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4"/>
       <c r="I10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M10" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="C1:C4"/>
@@ -1002,12 +973,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/KeHoachBaoDamQuanY.xlsx
+++ b/Resources/Sheet/KeHoachBaoDamQuanY.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B065D0-6FC8-46FF-80D3-13890BDA0152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02123478-3210-4B8C-A422-66EF5854177E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeHoachBaoDamQuanY" sheetId="12" r:id="rId1"/>
@@ -33,26 +33,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>%QS</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
     <t>Nội dung</t>
   </si>
   <si>
     <t>Quân số</t>
   </si>
   <si>
-    <t>Dự kiến tỷ lệ TBB</t>
-  </si>
-  <si>
     <t>Phân bổ chuyển thương</t>
   </si>
   <si>
@@ -74,38 +65,41 @@
     <t>Tổng</t>
   </si>
   <si>
-    <t>Số người</t>
-  </si>
-  <si>
     <t>TBHH</t>
   </si>
   <si>
-    <t>Người</t>
-  </si>
-  <si>
     <t>Toàn trận</t>
   </si>
   <si>
-    <t>Hướng chủ yếu</t>
-  </si>
-  <si>
-    <t>Hướng thứ yếu</t>
-  </si>
-  <si>
-    <t>Phòng ngự phía sau</t>
-  </si>
-  <si>
-    <t>LL còn lại</t>
-  </si>
-  <si>
     <t>Ngày cao nhất</t>
+  </si>
+  <si>
+    <t>Dự kiến tỷ lệ TBBB</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>%TB</t>
+  </si>
+  <si>
+    <t>HCY</t>
+  </si>
+  <si>
+    <t>HTY</t>
+  </si>
+  <si>
+    <t>PNPS</t>
+  </si>
+  <si>
+    <t>LLCL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,23 +121,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,19 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,53 +246,53 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -598,381 +565,391 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C05F80-CC1F-4AFA-9FAB-E49B7233EB8A}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="12" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="14"/>
+      <c r="J2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="15" t="s">
+    <row r="3" spans="1:12">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="16"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>12</v>
+      <c r="B5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1">
+        <f>ROUND(B5*C5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" ref="F5:F10" si="0">ROUND(D5*E5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H10" si="1">ROUND(G5*B5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <f>D5+H5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <f>ROUNDUP(I5/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <f>I5-J5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <f>I5</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <f>ROUND(B6*C6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" ref="I6:I10" si="2">D6+H6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" ref="J6:J10" si="3">ROUNDUP(I6/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" ref="K6:K10" si="4">I6-J6</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" ref="L6:L10" si="5">I6</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1">
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1">
         <v>-1</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="1">
-        <f>ROUND(C5*D5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="1">
-        <f>ROUND(E5*F5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="1">
-        <f>ROUND(H5*C5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <f>ROUND(E5+I5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <f>ROUNDUP(J5/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <f>J5-K5</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <f>J5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24">
-      <c r="A6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="1">
-        <f t="shared" ref="E6:E10" si="0">ROUND(C6*D6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="1">
-        <f t="shared" ref="G6:G10" si="1">ROUND(E6*F6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="1">
-        <f t="shared" ref="I6:I10" si="2">ROUND(H6*C6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <f t="shared" ref="J6:J10" si="3">ROUND(E6+I6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <f t="shared" ref="K6:K10" si="4">ROUNDUP(J6/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <f t="shared" ref="L6:L10" si="5">J6-K6</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <f t="shared" ref="M6:M10" si="6">J6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24">
-      <c r="A7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="1">
+      <c r="C7" s="2">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <f>ROUND(B7*C7/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="4"/>
       <c r="I7" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M7" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:13" ht="24">
-      <c r="A8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1">
+    <row r="8" spans="1:12">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1">
         <v>-1</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="1">
+      <c r="C8" s="2">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1">
+        <f>ROUND(B8*C8/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="4"/>
       <c r="I8" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M8" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C9" s="1">
+        <f>ROUND(D9/B9*100,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <f>D5-D6-D7-D8</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <v>20</v>
       </c>
-      <c r="C9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D9" s="1">
-        <f>ROUND(E9/C9*100,1)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <f>E5-E6-E7-E8</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="1">
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="4"/>
       <c r="I9" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:13" ht="24">
-      <c r="A10" s="3">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="1">
-        <f>C5</f>
+    <row r="10" spans="1:12">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
+        <f>B5</f>
         <v>-1</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1">
+      <c r="C10" s="2">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
+        <f>ROUND(B10*C10/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="4"/>
       <c r="I10" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
+  <mergeCells count="15">
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:C4"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
